--- a/Output/Dataframes/phenotypes.xlsx
+++ b/Output/Dataframes/phenotypes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1843" uniqueCount="133">
   <si>
     <t>sample_id</t>
   </si>
@@ -28,67 +28,64 @@
     <t>genotype</t>
   </si>
   <si>
-    <t>D402000259</t>
-  </si>
-  <si>
-    <t>D402000265</t>
-  </si>
-  <si>
-    <t>D402007216</t>
-  </si>
-  <si>
-    <t>D402007217</t>
-  </si>
-  <si>
-    <t>D402007228</t>
-  </si>
-  <si>
-    <t>D402007237</t>
-  </si>
-  <si>
-    <t>D402007245</t>
-  </si>
-  <si>
-    <t>D402007247</t>
-  </si>
-  <si>
-    <t>D402007248</t>
-  </si>
-  <si>
-    <t>D402007259</t>
-  </si>
-  <si>
-    <t>D402007279</t>
-  </si>
-  <si>
-    <t>D402007284</t>
-  </si>
-  <si>
-    <t>D402007285</t>
-  </si>
-  <si>
-    <t>D402007290</t>
-  </si>
-  <si>
-    <t>D402007293</t>
-  </si>
-  <si>
-    <t>D402007304</t>
-  </si>
-  <si>
-    <t>D402007305</t>
-  </si>
-  <si>
-    <t>D402007310</t>
-  </si>
-  <si>
-    <t>D402007314</t>
-  </si>
-  <si>
-    <t>D402007363</t>
-  </si>
-  <si>
-    <t>D402007364</t>
+    <t>D402007236</t>
+  </si>
+  <si>
+    <t>D402007296</t>
+  </si>
+  <si>
+    <t>D402007306</t>
+  </si>
+  <si>
+    <t>D402007307</t>
+  </si>
+  <si>
+    <t>D402007323</t>
+  </si>
+  <si>
+    <t>D402007324</t>
+  </si>
+  <si>
+    <t>D402007332</t>
+  </si>
+  <si>
+    <t>D402007333</t>
+  </si>
+  <si>
+    <t>D402007335</t>
+  </si>
+  <si>
+    <t>D402007340</t>
+  </si>
+  <si>
+    <t>D402007341</t>
+  </si>
+  <si>
+    <t>D402007344</t>
+  </si>
+  <si>
+    <t>D402007345</t>
+  </si>
+  <si>
+    <t>D402007349</t>
+  </si>
+  <si>
+    <t>D402007350</t>
+  </si>
+  <si>
+    <t>D402007351</t>
+  </si>
+  <si>
+    <t>D402007352</t>
+  </si>
+  <si>
+    <t>D402007354</t>
+  </si>
+  <si>
+    <t>D402007360</t>
+  </si>
+  <si>
+    <t>D402007365</t>
   </si>
   <si>
     <t>CACNA1S</t>
@@ -172,67 +169,49 @@
     <t>IM</t>
   </si>
   <si>
+    <t>PM</t>
+  </si>
+  <si>
     <t>NM_or_IM</t>
   </si>
   <si>
-    <t>NM,IM,IM</t>
-  </si>
-  <si>
-    <t>PM</t>
+    <t>FavorableResponseGenotype</t>
+  </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>IA,SA</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>IM,NM_or_IM</t>
+  </si>
+  <si>
+    <t>IA</t>
   </si>
   <si>
     <t>UnfavorableResponseGenotype</t>
   </si>
   <si>
-    <t>RA</t>
-  </si>
-  <si>
     <t>SA</t>
   </si>
   <si>
     <t>RM</t>
   </si>
   <si>
-    <t>DF</t>
-  </si>
-  <si>
-    <t>IA</t>
-  </si>
-  <si>
-    <t>FavorableResponseGenotype</t>
-  </si>
-  <si>
-    <t>IA,SA</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>IM,NM_or_IM</t>
-  </si>
-  <si>
-    <t>Indeterminate,Indeterminate,Indeterminate,Indeterminate,Indeterminate,Indeterminate,Indeterminate,Indeterminate,Indeterminate,Deficient,Deficient,Deficient,Deficient,Deficient,Deficient</t>
-  </si>
-  <si>
-    <t>Indeterminate,MHS,MHS</t>
-  </si>
-  <si>
-    <t>IM,unknown</t>
-  </si>
-  <si>
-    <t>IM,IM,NM_or_IM,NM_or_IM</t>
-  </si>
-  <si>
-    <t>MHS</t>
-  </si>
-  <si>
-    <t>Indeterminate,Indeterminate,Deficient</t>
-  </si>
-  <si>
-    <t>Indeterminate,MHS,MHS,MHS,MHS,MHS</t>
-  </si>
-  <si>
-    <t>NM,NM_or_IM</t>
+    <t>IM,PM</t>
+  </si>
+  <si>
+    <t>NM,NM_or_IM,NM_or_IM</t>
+  </si>
+  <si>
+    <t>NM,RM,UM</t>
+  </si>
+  <si>
+    <t>NM,IM,PM</t>
   </si>
   <si>
     <t>WT/WT</t>
@@ -241,208 +220,199 @@
     <t>*1F/*1F</t>
   </si>
   <si>
+    <t>*1/*4</t>
+  </si>
+  <si>
+    <t>*6/*6</t>
+  </si>
+  <si>
+    <t>*1A/*1C</t>
+  </si>
+  <si>
     <t>*1/*1</t>
   </si>
   <si>
+    <t>*1/*35</t>
+  </si>
+  <si>
+    <t>*2/*2</t>
+  </si>
+  <si>
+    <t>*1B/*1B</t>
+  </si>
+  <si>
+    <t>*3/*3</t>
+  </si>
+  <si>
+    <t>c.=/c.=</t>
+  </si>
+  <si>
+    <t>B/B</t>
+  </si>
+  <si>
+    <t>*A/*A</t>
+  </si>
+  <si>
+    <t>rs12979860C/rs12979860C</t>
+  </si>
+  <si>
+    <t>Null/m.=</t>
+  </si>
+  <si>
+    <t>*4/*4</t>
+  </si>
+  <si>
+    <t>*4/*5E,*5/*6</t>
+  </si>
+  <si>
+    <t>*1/*60</t>
+  </si>
+  <si>
+    <t>*1/*2</t>
+  </si>
+  <si>
+    <t>*1A/*1A</t>
+  </si>
+  <si>
+    <t>*1/*2+3,*2/*3</t>
+  </si>
+  <si>
+    <t>B/Null</t>
+  </si>
+  <si>
+    <t>*4/*5</t>
+  </si>
+  <si>
+    <t>*2/*6</t>
+  </si>
+  <si>
+    <t>*1/*3</t>
+  </si>
+  <si>
+    <t>*A/*B</t>
+  </si>
+  <si>
+    <t>rs12979860C/rs12979860T</t>
+  </si>
+  <si>
+    <t>*5/*5</t>
+  </si>
+  <si>
+    <t>*1B/*5A+7A+1B</t>
+  </si>
+  <si>
+    <t>*4/*6</t>
+  </si>
+  <si>
+    <t>*1A/*1F</t>
+  </si>
+  <si>
+    <t>*1/*1H</t>
+  </si>
+  <si>
     <t>*1/*6</t>
   </si>
   <si>
+    <t>*1A/*1B</t>
+  </si>
+  <si>
+    <t>*1/*17</t>
+  </si>
+  <si>
+    <t>*2+3/*2+3</t>
+  </si>
+  <si>
+    <t>*B/*C</t>
+  </si>
+  <si>
+    <t>*4/*7</t>
+  </si>
+  <si>
+    <t>*1/*9</t>
+  </si>
+  <si>
+    <t>*1/*5</t>
+  </si>
+  <si>
+    <t>rs12979860T/rs12979860T</t>
+  </si>
+  <si>
+    <t>*1/*13,*6/*8</t>
+  </si>
+  <si>
+    <t>*1B/*4+1C</t>
+  </si>
+  <si>
+    <t>*1/*28+60+80+93</t>
+  </si>
+  <si>
+    <t>*28+60+80+93/*60</t>
+  </si>
+  <si>
+    <t>*1/*14</t>
+  </si>
+  <si>
+    <t>*A/*C</t>
+  </si>
+  <si>
     <t>*1A/*3</t>
   </si>
   <si>
-    <t>*1/*2</t>
-  </si>
-  <si>
-    <t>*1/*1,*1/*27,*27/*27</t>
-  </si>
-  <si>
-    <t>*1B/*1B</t>
-  </si>
-  <si>
-    <t>*3/*3</t>
-  </si>
-  <si>
-    <t>c.=/c.=</t>
-  </si>
-  <si>
-    <t>B/Null</t>
-  </si>
-  <si>
-    <t>*B/*C</t>
-  </si>
-  <si>
-    <t>rs12979860T/rs12979860T</t>
-  </si>
-  <si>
-    <t>Null/m.=</t>
-  </si>
-  <si>
-    <t>*4/*4</t>
-  </si>
-  <si>
-    <t>*5/*5</t>
-  </si>
-  <si>
-    <t>*1A/*1F</t>
-  </si>
-  <si>
-    <t>*1/*4</t>
-  </si>
-  <si>
-    <t>*1A/*1C</t>
-  </si>
-  <si>
-    <t>*1/*4B</t>
+    <t>*7A/*7A+1B,*7A/*7C+1B,*7A+1B/*7C</t>
+  </si>
+  <si>
+    <t>*1/*22</t>
+  </si>
+  <si>
+    <t>*1/*1,*1/*17,*17/*17</t>
+  </si>
+  <si>
+    <t>*1/*45</t>
+  </si>
+  <si>
+    <t>*1/*3C</t>
+  </si>
+  <si>
+    <t>*1/*1,*1/*15,*15/*15</t>
   </si>
   <si>
     <t>*2/*4</t>
   </si>
   <si>
-    <t>*1B/*5A+7A+1B</t>
-  </si>
-  <si>
-    <t>*1/*3</t>
-  </si>
-  <si>
-    <t>B/Serres</t>
-  </si>
-  <si>
-    <t>*A/*A</t>
-  </si>
-  <si>
-    <t>rs12979860C/rs12979860T</t>
-  </si>
-  <si>
-    <t>*1/*28+60+80+93</t>
-  </si>
-  <si>
-    <t>F508delCTT/WT</t>
-  </si>
-  <si>
-    <t>*1A/*1A</t>
-  </si>
-  <si>
-    <t>*1/*10</t>
-  </si>
-  <si>
-    <t>B/B</t>
-  </si>
-  <si>
-    <t>*4/*5</t>
+    <t>*1B/*3</t>
+  </si>
+  <si>
+    <t>*B/*B</t>
+  </si>
+  <si>
+    <t>*1B/*1C</t>
+  </si>
+  <si>
+    <t>*7B/*7C+1B</t>
+  </si>
+  <si>
+    <t>c.1129-5923C&gt;G/c.=</t>
+  </si>
+  <si>
+    <t>*4/*6J,*6/*7</t>
+  </si>
+  <si>
+    <t>*28+60+80/*28+60+80+93</t>
   </si>
   <si>
     <t>*60/*60</t>
   </si>
   <si>
-    <t>*A/*B</t>
-  </si>
-  <si>
-    <t>*28+60+80+93/*28+60+80+93</t>
-  </si>
-  <si>
-    <t>*2/*2</t>
-  </si>
-  <si>
-    <t>*4/*6</t>
-  </si>
-  <si>
-    <t>*1A/*7A+1B,*1B/*7A</t>
-  </si>
-  <si>
-    <t>rs12979860C/rs12979860C</t>
-  </si>
-  <si>
-    <t>*28+60+80+93/*60</t>
-  </si>
-  <si>
-    <t>*1/*22</t>
-  </si>
-  <si>
-    <t>c.1129-5923C&gt;G/c.=</t>
-  </si>
-  <si>
-    <t>*4/*5E,*5/*6</t>
-  </si>
-  <si>
-    <t>*1/*60</t>
-  </si>
-  <si>
-    <t>*1/*2+3,*2/*3</t>
-  </si>
-  <si>
-    <t>B/B,Val77Leu/B,B/Roubaix,B/Serres,B/Nashville,Val77Leu/Val77Leu,Val77Leu/Roubaix,Val77Leu/Serres,Val77Leu/Nashville,Roubaix/Roubaix,Roubaix/Serres,Nashville/Roubaix,Serres/Serres,Nashville/Serres,Nashville/Nashville</t>
-  </si>
-  <si>
-    <t>WT/WT,c.6487C&gt;T/WT,c.6487C&gt;T/c.6487C&gt;T</t>
-  </si>
-  <si>
-    <t>*1/*28+60+80,*28/*60+80</t>
-  </si>
-  <si>
-    <t>*6/*6</t>
-  </si>
-  <si>
-    <t>*1/*9</t>
-  </si>
-  <si>
-    <t>*4B/*4B</t>
-  </si>
-  <si>
-    <t>*4/*35</t>
-  </si>
-  <si>
-    <t>*1H/*9</t>
-  </si>
-  <si>
-    <t>*2/*33</t>
-  </si>
-  <si>
-    <t>*2+3/*3</t>
-  </si>
-  <si>
-    <t>*B/*B</t>
-  </si>
-  <si>
-    <t>*1/*5</t>
-  </si>
-  <si>
-    <t>*A/*C</t>
-  </si>
-  <si>
-    <t>*1/*3,*1/*2+3,*2/*3,*2/*2+3</t>
-  </si>
-  <si>
-    <t>*1A/*4+1C</t>
-  </si>
-  <si>
-    <t>c.1840C&gt;T/WT</t>
-  </si>
-  <si>
-    <t>*2/*4B</t>
-  </si>
-  <si>
-    <t>*3/*22</t>
-  </si>
-  <si>
-    <t>*1/*14</t>
-  </si>
-  <si>
-    <t>*3/*3,*2+3/*3,*2+3/*2+3</t>
-  </si>
-  <si>
-    <t>*1B/*7B</t>
-  </si>
-  <si>
-    <t>B/B,B/Nashville,Nashville/Nashville</t>
-  </si>
-  <si>
-    <t>WT/WT,c.6487C&gt;T/WT,c.14545G&gt;A/WT,c.6487C&gt;T/c.6487C&gt;T,c.6487C&gt;T/c.14545G&gt;A,c.14545G&gt;A/c.14545G&gt;A</t>
-  </si>
-  <si>
-    <t>*1A/*1F,*1F/*8</t>
-  </si>
-  <si>
-    <t>*2/*35</t>
+    <t>*1F/*1K</t>
+  </si>
+  <si>
+    <t>*1/*7,*5/*6</t>
+  </si>
+  <si>
+    <t>*1/*3A,*3B/*3C</t>
+  </si>
+  <si>
+    <t>*7A+1B/*7C+1B</t>
   </si>
 </sst>
 </file>
@@ -800,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E484"/>
+  <dimension ref="A1:E461"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -825,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -842,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -859,13 +829,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -876,13 +846,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -893,13 +863,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -910,13 +880,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -927,13 +897,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -944,13 +914,13 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -961,13 +931,13 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -978,13 +948,13 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -995,13 +965,13 @@
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1012,13 +982,13 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1029,13 +999,13 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1046,13 +1016,13 @@
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1063,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1080,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1097,13 +1067,13 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1114,13 +1084,13 @@
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1131,13 +1101,13 @@
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1148,13 +1118,13 @@
         <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1165,13 +1135,13 @@
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1182,13 +1152,13 @@
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1199,13 +1169,13 @@
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1216,13 +1186,13 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1233,13 +1203,13 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1250,13 +1220,13 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1267,13 +1237,10 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1284,13 +1251,13 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1301,13 +1268,13 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1318,13 +1285,13 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1335,13 +1302,13 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1352,13 +1319,13 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1369,13 +1336,13 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1386,13 +1353,13 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1403,13 +1370,13 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1420,13 +1387,13 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1437,13 +1404,13 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E38" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1454,13 +1421,13 @@
         <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1471,13 +1438,13 @@
         <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1488,13 +1455,13 @@
         <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1505,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1522,13 +1489,13 @@
         <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1539,13 +1506,13 @@
         <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1556,13 +1523,13 @@
         <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1573,13 +1540,13 @@
         <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E46" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1590,13 +1557,13 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E47" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1607,13 +1574,13 @@
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1624,13 +1591,13 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1641,13 +1608,13 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1658,13 +1625,13 @@
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1675,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
         <v>50</v>
       </c>
       <c r="E52" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1692,13 +1659,13 @@
         <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1709,13 +1676,13 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1726,13 +1693,13 @@
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
         <v>50</v>
       </c>
       <c r="E55" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1743,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E56" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1760,13 +1727,13 @@
         <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1777,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E58" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1794,13 +1761,13 @@
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E59" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1811,13 +1778,13 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E60" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1828,13 +1795,13 @@
         <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E61" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1845,13 +1812,13 @@
         <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E62" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1862,13 +1829,13 @@
         <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E63" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1879,13 +1846,13 @@
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E64" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1896,13 +1863,13 @@
         <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1913,13 +1880,13 @@
         <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D66" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E66" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1930,13 +1897,13 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D67" t="s">
         <v>60</v>
       </c>
       <c r="E67" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1947,13 +1914,13 @@
         <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E68" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1964,13 +1931,13 @@
         <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D69" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E69" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1981,13 +1948,13 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D70" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E70" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1998,13 +1965,13 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E71" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2015,13 +1982,13 @@
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2032,13 +1999,13 @@
         <v>7</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E73" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2049,13 +2016,13 @@
         <v>7</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E74" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2066,13 +2033,13 @@
         <v>7</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D75" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E75" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2083,13 +2050,13 @@
         <v>7</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E76" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2100,13 +2067,13 @@
         <v>7</v>
       </c>
       <c r="C77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2117,13 +2084,13 @@
         <v>7</v>
       </c>
       <c r="C78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E78" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2134,13 +2101,13 @@
         <v>7</v>
       </c>
       <c r="C79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D79" t="s">
         <v>50</v>
       </c>
       <c r="E79" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2151,13 +2118,13 @@
         <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D80" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E80" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2168,13 +2135,13 @@
         <v>7</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E81" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2185,13 +2152,13 @@
         <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D82" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E82" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2202,13 +2169,13 @@
         <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D83" t="s">
         <v>50</v>
       </c>
       <c r="E83" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2219,13 +2186,13 @@
         <v>7</v>
       </c>
       <c r="C84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D84" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E84" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2236,13 +2203,13 @@
         <v>7</v>
       </c>
       <c r="C85" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E85" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2253,13 +2220,13 @@
         <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D86" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E86" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2270,13 +2237,13 @@
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E87" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2287,13 +2254,13 @@
         <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E88" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2304,13 +2271,13 @@
         <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D89" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E89" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2321,13 +2288,13 @@
         <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D90" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E90" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2338,13 +2305,13 @@
         <v>7</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E91" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2355,13 +2322,13 @@
         <v>7</v>
       </c>
       <c r="C92" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D92" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E92" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2372,13 +2339,13 @@
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D93" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E93" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2389,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E94" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2406,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D95" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E95" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2423,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E96" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2440,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
         <v>50</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2457,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D98" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E98" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2474,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D99" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E99" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2491,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D100" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E100" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2508,13 +2475,13 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E101" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2525,13 +2492,13 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E102" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2542,13 +2509,13 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E103" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2559,13 +2526,13 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D104" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E104" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2576,13 +2543,13 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D105" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E105" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2593,13 +2560,13 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D106" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E106" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2610,13 +2577,13 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E107" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2627,13 +2594,13 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E108" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2644,13 +2611,13 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D109" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E109" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2661,13 +2628,13 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D110" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E110" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2678,13 +2645,13 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D111" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E111" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2695,13 +2662,13 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E112" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2712,13 +2679,13 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D113" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E113" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2729,13 +2696,13 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E114" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2746,13 +2713,13 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D115" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E115" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2763,13 +2730,13 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D116" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E116" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2780,13 +2747,13 @@
         <v>9</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E117" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2797,13 +2764,13 @@
         <v>9</v>
       </c>
       <c r="C118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D118" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E118" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2814,13 +2781,13 @@
         <v>9</v>
       </c>
       <c r="C119" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E119" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2831,13 +2798,13 @@
         <v>9</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D120" t="s">
         <v>50</v>
       </c>
       <c r="E120" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2848,13 +2815,13 @@
         <v>9</v>
       </c>
       <c r="C121" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D121" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E121" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2865,13 +2832,13 @@
         <v>9</v>
       </c>
       <c r="C122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D122" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E122" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2882,13 +2849,13 @@
         <v>9</v>
       </c>
       <c r="C123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E123" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2899,13 +2866,13 @@
         <v>9</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D124" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E124" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2916,13 +2883,13 @@
         <v>9</v>
       </c>
       <c r="C125" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D125" t="s">
         <v>50</v>
       </c>
       <c r="E125" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2933,13 +2900,13 @@
         <v>9</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D126" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E126" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2950,13 +2917,13 @@
         <v>9</v>
       </c>
       <c r="C127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D127" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E127" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2967,13 +2934,13 @@
         <v>9</v>
       </c>
       <c r="C128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D128" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E128" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2984,13 +2951,13 @@
         <v>9</v>
       </c>
       <c r="C129" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D129" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E129" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3001,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="C130" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D130" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E130" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3018,13 +2985,13 @@
         <v>9</v>
       </c>
       <c r="C131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E131" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3035,13 +3002,13 @@
         <v>9</v>
       </c>
       <c r="C132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D132" t="s">
         <v>52</v>
       </c>
       <c r="E132" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3052,13 +3019,13 @@
         <v>9</v>
       </c>
       <c r="C133" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D133" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E133" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3069,13 +3036,13 @@
         <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D134" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E134" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3086,13 +3053,13 @@
         <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D135" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E135" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3103,13 +3070,13 @@
         <v>9</v>
       </c>
       <c r="C136" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D136" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E136" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3120,13 +3087,13 @@
         <v>9</v>
       </c>
       <c r="C137" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D137" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E137" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3137,13 +3104,13 @@
         <v>9</v>
       </c>
       <c r="C138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D138" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E138" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3154,13 +3121,13 @@
         <v>9</v>
       </c>
       <c r="C139" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D139" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E139" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3171,13 +3138,13 @@
         <v>10</v>
       </c>
       <c r="C140" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D140" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E140" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3188,13 +3155,13 @@
         <v>10</v>
       </c>
       <c r="C141" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E141" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3205,13 +3172,13 @@
         <v>10</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D142" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E142" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3222,13 +3189,13 @@
         <v>10</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D143" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E143" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3239,13 +3206,13 @@
         <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D144" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E144" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3256,13 +3223,13 @@
         <v>10</v>
       </c>
       <c r="C145" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D145" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E145" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3273,13 +3240,13 @@
         <v>10</v>
       </c>
       <c r="C146" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D146" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E146" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3290,13 +3257,13 @@
         <v>10</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E147" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3307,13 +3274,13 @@
         <v>10</v>
       </c>
       <c r="C148" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D148" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E148" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3324,13 +3291,13 @@
         <v>10</v>
       </c>
       <c r="C149" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D149" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E149" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3341,13 +3308,13 @@
         <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D150" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E150" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3358,13 +3325,13 @@
         <v>10</v>
       </c>
       <c r="C151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D151" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E151" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3375,13 +3342,13 @@
         <v>10</v>
       </c>
       <c r="C152" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D152" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E152" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3392,13 +3359,13 @@
         <v>10</v>
       </c>
       <c r="C153" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D153" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E153" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3409,13 +3376,13 @@
         <v>10</v>
       </c>
       <c r="C154" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D154" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E154" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3426,13 +3393,13 @@
         <v>10</v>
       </c>
       <c r="C155" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D155" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E155" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3443,13 +3410,13 @@
         <v>10</v>
       </c>
       <c r="C156" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D156" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E156" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3460,13 +3427,13 @@
         <v>10</v>
       </c>
       <c r="C157" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D157" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E157" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3477,13 +3444,13 @@
         <v>10</v>
       </c>
       <c r="C158" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D158" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E158" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3494,13 +3461,13 @@
         <v>10</v>
       </c>
       <c r="C159" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D159" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E159" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3511,13 +3478,13 @@
         <v>10</v>
       </c>
       <c r="C160" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D160" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E160" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3528,13 +3495,13 @@
         <v>10</v>
       </c>
       <c r="C161" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D161" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E161" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3545,13 +3512,13 @@
         <v>10</v>
       </c>
       <c r="C162" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D162" t="s">
         <v>50</v>
       </c>
       <c r="E162" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3562,13 +3529,13 @@
         <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D163" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E163" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3579,13 +3546,13 @@
         <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D164" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E164" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3596,13 +3563,13 @@
         <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D165" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E165" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3613,13 +3580,13 @@
         <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D166" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E166" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3630,13 +3597,13 @@
         <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D167" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E167" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3647,13 +3614,13 @@
         <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D168" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E168" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3664,10 +3631,13 @@
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D169" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="E169" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3678,13 +3648,13 @@
         <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D170" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E170" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3695,13 +3665,13 @@
         <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D171" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E171" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3712,13 +3682,13 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D172" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E172" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3729,13 +3699,13 @@
         <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D173" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E173" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3746,13 +3716,13 @@
         <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D174" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E174" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3763,13 +3733,13 @@
         <v>11</v>
       </c>
       <c r="C175" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D175" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E175" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3780,13 +3750,13 @@
         <v>11</v>
       </c>
       <c r="C176" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D176" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E176" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3797,13 +3767,13 @@
         <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D177" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E177" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3814,13 +3784,13 @@
         <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D178" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E178" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3831,13 +3801,13 @@
         <v>11</v>
       </c>
       <c r="C179" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D179" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E179" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3848,13 +3818,13 @@
         <v>11</v>
       </c>
       <c r="C180" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D180" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E180" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3865,13 +3835,13 @@
         <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D181" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E181" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3882,13 +3852,13 @@
         <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D182" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E182" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3899,13 +3869,13 @@
         <v>11</v>
       </c>
       <c r="C183" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D183" t="s">
+        <v>47</v>
+      </c>
+      <c r="E183" t="s">
         <v>66</v>
-      </c>
-      <c r="E183" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3916,13 +3886,13 @@
         <v>11</v>
       </c>
       <c r="C184" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D184" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E184" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3933,13 +3903,13 @@
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D185" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="E185" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3950,13 +3920,13 @@
         <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D186" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E186" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3967,13 +3937,13 @@
         <v>12</v>
       </c>
       <c r="C187" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E187" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3984,13 +3954,13 @@
         <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D188" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E188" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4001,13 +3971,13 @@
         <v>12</v>
       </c>
       <c r="C189" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D189" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E189" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4018,13 +3988,13 @@
         <v>12</v>
       </c>
       <c r="C190" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D190" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E190" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4035,13 +4005,13 @@
         <v>12</v>
       </c>
       <c r="C191" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D191" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E191" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4052,13 +4022,13 @@
         <v>12</v>
       </c>
       <c r="C192" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D192" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E192" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4069,13 +4039,13 @@
         <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D193" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E193" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4086,13 +4056,13 @@
         <v>12</v>
       </c>
       <c r="C194" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D194" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E194" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4103,13 +4073,13 @@
         <v>12</v>
       </c>
       <c r="C195" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D195" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E195" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4120,13 +4090,13 @@
         <v>12</v>
       </c>
       <c r="C196" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D196" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E196" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4137,13 +4107,13 @@
         <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D197" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E197" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4154,13 +4124,13 @@
         <v>12</v>
       </c>
       <c r="C198" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D198" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E198" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4171,13 +4141,13 @@
         <v>12</v>
       </c>
       <c r="C199" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D199" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E199" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4188,13 +4158,13 @@
         <v>12</v>
       </c>
       <c r="C200" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D200" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E200" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4205,13 +4175,13 @@
         <v>12</v>
       </c>
       <c r="C201" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D201" t="s">
         <v>52</v>
       </c>
       <c r="E201" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -4222,13 +4192,13 @@
         <v>12</v>
       </c>
       <c r="C202" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D202" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E202" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -4239,13 +4209,13 @@
         <v>12</v>
       </c>
       <c r="C203" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D203" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E203" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -4256,13 +4226,13 @@
         <v>12</v>
       </c>
       <c r="C204" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D204" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E204" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -4273,13 +4243,13 @@
         <v>12</v>
       </c>
       <c r="C205" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D205" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E205" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -4290,13 +4260,13 @@
         <v>12</v>
       </c>
       <c r="C206" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D206" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E206" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -4307,13 +4277,13 @@
         <v>12</v>
       </c>
       <c r="C207" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D207" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E207" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -4324,13 +4294,13 @@
         <v>12</v>
       </c>
       <c r="C208" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D208" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E208" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -4341,13 +4311,13 @@
         <v>13</v>
       </c>
       <c r="C209" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D209" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E209" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -4358,13 +4328,13 @@
         <v>13</v>
       </c>
       <c r="C210" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E210" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -4375,13 +4345,13 @@
         <v>13</v>
       </c>
       <c r="C211" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D211" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E211" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -4392,13 +4362,13 @@
         <v>13</v>
       </c>
       <c r="C212" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D212" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E212" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -4409,13 +4379,13 @@
         <v>13</v>
       </c>
       <c r="C213" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D213" t="s">
         <v>50</v>
       </c>
       <c r="E213" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -4426,13 +4396,13 @@
         <v>13</v>
       </c>
       <c r="C214" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D214" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E214" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4443,13 +4413,13 @@
         <v>13</v>
       </c>
       <c r="C215" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D215" t="s">
         <v>50</v>
       </c>
       <c r="E215" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4460,13 +4430,13 @@
         <v>13</v>
       </c>
       <c r="C216" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D216" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E216" t="s">
-        <v>123</v>
+        <v>71</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4477,13 +4447,13 @@
         <v>13</v>
       </c>
       <c r="C217" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D217" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E217" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4494,13 +4464,13 @@
         <v>13</v>
       </c>
       <c r="C218" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D218" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E218" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4511,13 +4481,13 @@
         <v>13</v>
       </c>
       <c r="C219" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D219" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E219" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4528,13 +4498,13 @@
         <v>13</v>
       </c>
       <c r="C220" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D220" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E220" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4545,13 +4515,13 @@
         <v>13</v>
       </c>
       <c r="C221" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D221" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E221" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4562,13 +4532,13 @@
         <v>13</v>
       </c>
       <c r="C222" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D222" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E222" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4579,13 +4549,13 @@
         <v>13</v>
       </c>
       <c r="C223" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D223" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E223" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4596,13 +4566,13 @@
         <v>13</v>
       </c>
       <c r="C224" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D224" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E224" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4613,13 +4583,13 @@
         <v>13</v>
       </c>
       <c r="C225" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D225" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E225" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4630,13 +4600,13 @@
         <v>13</v>
       </c>
       <c r="C226" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D226" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E226" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4647,13 +4617,13 @@
         <v>13</v>
       </c>
       <c r="C227" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D227" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E227" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4664,13 +4634,13 @@
         <v>13</v>
       </c>
       <c r="C228" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D228" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E228" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4681,13 +4651,13 @@
         <v>13</v>
       </c>
       <c r="C229" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D229" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E229" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4698,13 +4668,13 @@
         <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D230" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E230" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4715,13 +4685,13 @@
         <v>13</v>
       </c>
       <c r="C231" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D231" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E231" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4732,13 +4702,13 @@
         <v>14</v>
       </c>
       <c r="C232" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D232" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E232" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4749,13 +4719,13 @@
         <v>14</v>
       </c>
       <c r="C233" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D233" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E233" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4766,13 +4736,13 @@
         <v>14</v>
       </c>
       <c r="C234" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D234" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E234" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4783,13 +4753,13 @@
         <v>14</v>
       </c>
       <c r="C235" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D235" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E235" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4800,13 +4770,13 @@
         <v>14</v>
       </c>
       <c r="C236" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D236" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E236" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4817,13 +4787,13 @@
         <v>14</v>
       </c>
       <c r="C237" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D237" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E237" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4834,13 +4804,13 @@
         <v>14</v>
       </c>
       <c r="C238" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D238" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E238" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4851,13 +4821,13 @@
         <v>14</v>
       </c>
       <c r="C239" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D239" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E239" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4868,13 +4838,13 @@
         <v>14</v>
       </c>
       <c r="C240" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D240" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E240" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4885,13 +4855,13 @@
         <v>14</v>
       </c>
       <c r="C241" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D241" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E241" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4902,13 +4872,13 @@
         <v>14</v>
       </c>
       <c r="C242" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D242" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E242" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4919,13 +4889,13 @@
         <v>14</v>
       </c>
       <c r="C243" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D243" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E243" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4936,13 +4906,13 @@
         <v>14</v>
       </c>
       <c r="C244" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D244" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E244" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4953,13 +4923,13 @@
         <v>14</v>
       </c>
       <c r="C245" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D245" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E245" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4970,13 +4940,13 @@
         <v>14</v>
       </c>
       <c r="C246" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D246" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E246" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4987,13 +4957,13 @@
         <v>14</v>
       </c>
       <c r="C247" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D247" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E247" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -5004,13 +4974,13 @@
         <v>14</v>
       </c>
       <c r="C248" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D248" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E248" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -5021,13 +4991,13 @@
         <v>14</v>
       </c>
       <c r="C249" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D249" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E249" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -5038,13 +5008,13 @@
         <v>14</v>
       </c>
       <c r="C250" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D250" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E250" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -5055,13 +5025,13 @@
         <v>14</v>
       </c>
       <c r="C251" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D251" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E251" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -5072,13 +5042,13 @@
         <v>14</v>
       </c>
       <c r="C252" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D252" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E252" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -5089,13 +5059,13 @@
         <v>14</v>
       </c>
       <c r="C253" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D253" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E253" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -5106,13 +5076,13 @@
         <v>14</v>
       </c>
       <c r="C254" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D254" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E254" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -5123,13 +5093,13 @@
         <v>15</v>
       </c>
       <c r="C255" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D255" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E255" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -5140,13 +5110,13 @@
         <v>15</v>
       </c>
       <c r="C256" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D256" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E256" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -5157,13 +5127,13 @@
         <v>15</v>
       </c>
       <c r="C257" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D257" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E257" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -5174,13 +5144,13 @@
         <v>15</v>
       </c>
       <c r="C258" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D258" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E258" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -5191,13 +5161,13 @@
         <v>15</v>
       </c>
       <c r="C259" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D259" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E259" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -5208,13 +5178,13 @@
         <v>15</v>
       </c>
       <c r="C260" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D260" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E260" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -5225,13 +5195,13 @@
         <v>15</v>
       </c>
       <c r="C261" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D261" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E261" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -5242,13 +5212,13 @@
         <v>15</v>
       </c>
       <c r="C262" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D262" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E262" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -5259,13 +5229,13 @@
         <v>15</v>
       </c>
       <c r="C263" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D263" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E263" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -5276,13 +5246,13 @@
         <v>15</v>
       </c>
       <c r="C264" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D264" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E264" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -5293,13 +5263,13 @@
         <v>15</v>
       </c>
       <c r="C265" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D265" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E265" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -5310,13 +5280,13 @@
         <v>15</v>
       </c>
       <c r="C266" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D266" t="s">
         <v>51</v>
       </c>
       <c r="E266" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -5327,13 +5297,13 @@
         <v>15</v>
       </c>
       <c r="C267" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D267" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E267" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -5344,13 +5314,13 @@
         <v>15</v>
       </c>
       <c r="C268" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D268" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E268" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -5361,13 +5331,13 @@
         <v>15</v>
       </c>
       <c r="C269" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D269" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E269" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -5378,13 +5348,13 @@
         <v>15</v>
       </c>
       <c r="C270" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D270" t="s">
         <v>52</v>
       </c>
       <c r="E270" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -5395,13 +5365,13 @@
         <v>15</v>
       </c>
       <c r="C271" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D271" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E271" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -5412,13 +5382,13 @@
         <v>15</v>
       </c>
       <c r="C272" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D272" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E272" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -5429,13 +5399,13 @@
         <v>15</v>
       </c>
       <c r="C273" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D273" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E273" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5446,13 +5416,13 @@
         <v>15</v>
       </c>
       <c r="C274" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D274" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E274" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5463,13 +5433,13 @@
         <v>15</v>
       </c>
       <c r="C275" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D275" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E275" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5480,13 +5450,13 @@
         <v>15</v>
       </c>
       <c r="C276" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D276" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E276" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5497,13 +5467,13 @@
         <v>15</v>
       </c>
       <c r="C277" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D277" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E277" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5514,13 +5484,13 @@
         <v>16</v>
       </c>
       <c r="C278" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D278" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E278" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5531,13 +5501,13 @@
         <v>16</v>
       </c>
       <c r="C279" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D279" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E279" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5548,13 +5518,13 @@
         <v>16</v>
       </c>
       <c r="C280" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D280" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E280" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5565,13 +5535,13 @@
         <v>16</v>
       </c>
       <c r="C281" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D281" t="s">
         <v>50</v>
       </c>
       <c r="E281" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5582,13 +5552,13 @@
         <v>16</v>
       </c>
       <c r="C282" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D282" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E282" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5599,13 +5569,13 @@
         <v>16</v>
       </c>
       <c r="C283" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D283" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E283" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5616,13 +5586,13 @@
         <v>16</v>
       </c>
       <c r="C284" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D284" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E284" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5633,13 +5603,13 @@
         <v>16</v>
       </c>
       <c r="C285" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D285" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E285" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5650,13 +5620,13 @@
         <v>16</v>
       </c>
       <c r="C286" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D286" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E286" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5667,13 +5637,13 @@
         <v>16</v>
       </c>
       <c r="C287" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D287" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E287" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5684,13 +5654,13 @@
         <v>16</v>
       </c>
       <c r="C288" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D288" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E288" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5701,13 +5671,13 @@
         <v>16</v>
       </c>
       <c r="C289" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D289" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E289" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5718,13 +5688,13 @@
         <v>16</v>
       </c>
       <c r="C290" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D290" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E290" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5735,13 +5705,13 @@
         <v>16</v>
       </c>
       <c r="C291" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D291" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E291" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5752,13 +5722,13 @@
         <v>16</v>
       </c>
       <c r="C292" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D292" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E292" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5769,13 +5739,13 @@
         <v>16</v>
       </c>
       <c r="C293" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D293" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E293" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5786,13 +5756,13 @@
         <v>16</v>
       </c>
       <c r="C294" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D294" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E294" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5803,13 +5773,13 @@
         <v>16</v>
       </c>
       <c r="C295" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D295" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E295" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5820,13 +5790,13 @@
         <v>16</v>
       </c>
       <c r="C296" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D296" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E296" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5837,13 +5807,13 @@
         <v>16</v>
       </c>
       <c r="C297" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D297" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E297" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5854,13 +5824,13 @@
         <v>16</v>
       </c>
       <c r="C298" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D298" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E298" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5871,13 +5841,13 @@
         <v>16</v>
       </c>
       <c r="C299" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D299" t="s">
         <v>50</v>
       </c>
       <c r="E299" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5888,13 +5858,13 @@
         <v>16</v>
       </c>
       <c r="C300" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D300" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E300" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5905,13 +5875,13 @@
         <v>17</v>
       </c>
       <c r="C301" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D301" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E301" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5922,13 +5892,13 @@
         <v>17</v>
       </c>
       <c r="C302" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D302" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E302" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5939,13 +5909,13 @@
         <v>17</v>
       </c>
       <c r="C303" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D303" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E303" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5956,13 +5926,13 @@
         <v>17</v>
       </c>
       <c r="C304" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D304" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E304" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5973,13 +5943,13 @@
         <v>17</v>
       </c>
       <c r="C305" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D305" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E305" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5990,13 +5960,13 @@
         <v>17</v>
       </c>
       <c r="C306" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D306" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E306" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -6007,13 +5977,13 @@
         <v>17</v>
       </c>
       <c r="C307" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D307" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E307" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -6024,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="C308" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D308" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E308" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -6041,13 +6011,13 @@
         <v>17</v>
       </c>
       <c r="C309" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D309" t="s">
         <v>50</v>
       </c>
       <c r="E309" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -6058,13 +6028,13 @@
         <v>17</v>
       </c>
       <c r="C310" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D310" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E310" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -6075,13 +6045,13 @@
         <v>17</v>
       </c>
       <c r="C311" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D311" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E311" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -6092,13 +6062,13 @@
         <v>17</v>
       </c>
       <c r="C312" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D312" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E312" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -6109,13 +6079,13 @@
         <v>17</v>
       </c>
       <c r="C313" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D313" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="E313" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -6126,13 +6096,13 @@
         <v>17</v>
       </c>
       <c r="C314" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D314" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E314" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -6143,13 +6113,13 @@
         <v>17</v>
       </c>
       <c r="C315" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D315" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E315" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -6160,13 +6130,13 @@
         <v>17</v>
       </c>
       <c r="C316" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D316" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E316" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -6177,13 +6147,13 @@
         <v>17</v>
       </c>
       <c r="C317" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D317" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E317" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -6194,13 +6164,13 @@
         <v>17</v>
       </c>
       <c r="C318" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D318" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E318" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -6211,13 +6181,13 @@
         <v>17</v>
       </c>
       <c r="C319" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D319" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E319" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -6228,13 +6198,13 @@
         <v>17</v>
       </c>
       <c r="C320" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D320" t="s">
         <v>60</v>
       </c>
       <c r="E320" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -6245,13 +6215,13 @@
         <v>17</v>
       </c>
       <c r="C321" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D321" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E321" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -6262,13 +6232,13 @@
         <v>17</v>
       </c>
       <c r="C322" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D322" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E322" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -6279,13 +6249,13 @@
         <v>17</v>
       </c>
       <c r="C323" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D323" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E323" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -6296,13 +6266,13 @@
         <v>18</v>
       </c>
       <c r="C324" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D324" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E324" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -6313,13 +6283,13 @@
         <v>18</v>
       </c>
       <c r="C325" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D325" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E325" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -6330,13 +6300,13 @@
         <v>18</v>
       </c>
       <c r="C326" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D326" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E326" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -6347,13 +6317,13 @@
         <v>18</v>
       </c>
       <c r="C327" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D327" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E327" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -6364,13 +6334,13 @@
         <v>18</v>
       </c>
       <c r="C328" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D328" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E328" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -6381,13 +6351,13 @@
         <v>18</v>
       </c>
       <c r="C329" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D329" t="s">
         <v>52</v>
       </c>
       <c r="E329" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -6398,13 +6368,13 @@
         <v>18</v>
       </c>
       <c r="C330" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D330" t="s">
         <v>50</v>
       </c>
       <c r="E330" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -6415,13 +6385,13 @@
         <v>18</v>
       </c>
       <c r="C331" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D331" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E331" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -6432,13 +6402,13 @@
         <v>18</v>
       </c>
       <c r="C332" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D332" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E332" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6449,13 +6419,13 @@
         <v>18</v>
       </c>
       <c r="C333" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D333" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E333" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6466,13 +6436,13 @@
         <v>18</v>
       </c>
       <c r="C334" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D334" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E334" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6483,13 +6453,13 @@
         <v>18</v>
       </c>
       <c r="C335" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D335" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E335" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6500,13 +6470,13 @@
         <v>18</v>
       </c>
       <c r="C336" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D336" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E336" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6517,10 +6487,13 @@
         <v>18</v>
       </c>
       <c r="C337" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D337" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="E337" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6531,13 +6504,13 @@
         <v>18</v>
       </c>
       <c r="C338" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D338" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E338" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6548,13 +6521,13 @@
         <v>18</v>
       </c>
       <c r="C339" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D339" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E339" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6565,13 +6538,13 @@
         <v>18</v>
       </c>
       <c r="C340" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D340" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E340" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6582,13 +6555,13 @@
         <v>18</v>
       </c>
       <c r="C341" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D341" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E341" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6599,13 +6572,13 @@
         <v>18</v>
       </c>
       <c r="C342" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D342" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E342" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6616,13 +6589,13 @@
         <v>18</v>
       </c>
       <c r="C343" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D343" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E343" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6633,13 +6606,13 @@
         <v>18</v>
       </c>
       <c r="C344" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D344" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E344" t="s">
-        <v>133</v>
+        <v>66</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6650,13 +6623,13 @@
         <v>18</v>
       </c>
       <c r="C345" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D345" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E345" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6667,13 +6640,13 @@
         <v>18</v>
       </c>
       <c r="C346" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D346" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E346" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6684,13 +6657,13 @@
         <v>19</v>
       </c>
       <c r="C347" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D347" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E347" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6701,13 +6674,13 @@
         <v>19</v>
       </c>
       <c r="C348" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D348" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E348" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6718,13 +6691,13 @@
         <v>19</v>
       </c>
       <c r="C349" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D349" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E349" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6735,13 +6708,13 @@
         <v>19</v>
       </c>
       <c r="C350" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D350" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E350" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6752,13 +6725,13 @@
         <v>19</v>
       </c>
       <c r="C351" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D351" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E351" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6769,13 +6742,13 @@
         <v>19</v>
       </c>
       <c r="C352" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D352" t="s">
         <v>52</v>
       </c>
       <c r="E352" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6786,13 +6759,13 @@
         <v>19</v>
       </c>
       <c r="C353" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D353" t="s">
         <v>50</v>
       </c>
       <c r="E353" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6803,13 +6776,13 @@
         <v>19</v>
       </c>
       <c r="C354" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D354" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E354" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6820,13 +6793,13 @@
         <v>19</v>
       </c>
       <c r="C355" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D355" t="s">
         <v>50</v>
       </c>
       <c r="E355" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6837,13 +6810,13 @@
         <v>19</v>
       </c>
       <c r="C356" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D356" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E356" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6854,13 +6827,13 @@
         <v>19</v>
       </c>
       <c r="C357" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D357" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E357" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6871,13 +6844,13 @@
         <v>19</v>
       </c>
       <c r="C358" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D358" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E358" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6888,13 +6861,13 @@
         <v>19</v>
       </c>
       <c r="C359" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D359" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E359" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6905,13 +6878,13 @@
         <v>19</v>
       </c>
       <c r="C360" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D360" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E360" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6922,13 +6895,13 @@
         <v>19</v>
       </c>
       <c r="C361" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D361" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E361" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6939,13 +6912,13 @@
         <v>19</v>
       </c>
       <c r="C362" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D362" t="s">
         <v>50</v>
       </c>
       <c r="E362" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6956,13 +6929,13 @@
         <v>19</v>
       </c>
       <c r="C363" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D363" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E363" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6973,13 +6946,13 @@
         <v>19</v>
       </c>
       <c r="C364" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D364" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E364" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6990,13 +6963,13 @@
         <v>19</v>
       </c>
       <c r="C365" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D365" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E365" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -7007,13 +6980,13 @@
         <v>19</v>
       </c>
       <c r="C366" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D366" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E366" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -7024,13 +6997,13 @@
         <v>19</v>
       </c>
       <c r="C367" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D367" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E367" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -7041,13 +7014,13 @@
         <v>19</v>
       </c>
       <c r="C368" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D368" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E368" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -7058,13 +7031,13 @@
         <v>19</v>
       </c>
       <c r="C369" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D369" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E369" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -7075,13 +7048,13 @@
         <v>20</v>
       </c>
       <c r="C370" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D370" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E370" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -7092,13 +7065,13 @@
         <v>20</v>
       </c>
       <c r="C371" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D371" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E371" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -7109,13 +7082,13 @@
         <v>20</v>
       </c>
       <c r="C372" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D372" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E372" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -7126,13 +7099,13 @@
         <v>20</v>
       </c>
       <c r="C373" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D373" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E373" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -7143,13 +7116,13 @@
         <v>20</v>
       </c>
       <c r="C374" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D374" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E374" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -7160,13 +7133,13 @@
         <v>20</v>
       </c>
       <c r="C375" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D375" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E375" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -7177,13 +7150,13 @@
         <v>20</v>
       </c>
       <c r="C376" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D376" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E376" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -7194,13 +7167,13 @@
         <v>20</v>
       </c>
       <c r="C377" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D377" t="s">
         <v>50</v>
       </c>
       <c r="E377" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -7211,13 +7184,13 @@
         <v>20</v>
       </c>
       <c r="C378" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D378" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E378" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -7228,13 +7201,13 @@
         <v>20</v>
       </c>
       <c r="C379" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D379" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E379" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -7245,13 +7218,13 @@
         <v>20</v>
       </c>
       <c r="C380" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D380" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E380" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -7262,13 +7235,13 @@
         <v>20</v>
       </c>
       <c r="C381" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D381" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E381" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -7279,13 +7252,13 @@
         <v>20</v>
       </c>
       <c r="C382" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D382" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E382" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -7296,13 +7269,13 @@
         <v>20</v>
       </c>
       <c r="C383" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D383" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E383" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -7313,13 +7286,13 @@
         <v>20</v>
       </c>
       <c r="C384" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D384" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E384" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -7330,13 +7303,13 @@
         <v>20</v>
       </c>
       <c r="C385" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D385" t="s">
         <v>50</v>
       </c>
       <c r="E385" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -7347,13 +7320,13 @@
         <v>20</v>
       </c>
       <c r="C386" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D386" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E386" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -7364,13 +7337,13 @@
         <v>20</v>
       </c>
       <c r="C387" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D387" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E387" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -7381,13 +7354,13 @@
         <v>20</v>
       </c>
       <c r="C388" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D388" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E388" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -7398,13 +7371,13 @@
         <v>20</v>
       </c>
       <c r="C389" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D389" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E389" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -7415,13 +7388,13 @@
         <v>20</v>
       </c>
       <c r="C390" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D390" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E390" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7432,13 +7405,13 @@
         <v>20</v>
       </c>
       <c r="C391" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D391" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E391" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7449,13 +7422,13 @@
         <v>20</v>
       </c>
       <c r="C392" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D392" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E392" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7466,13 +7439,13 @@
         <v>21</v>
       </c>
       <c r="C393" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D393" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E393" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7483,13 +7456,13 @@
         <v>21</v>
       </c>
       <c r="C394" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D394" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E394" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7500,13 +7473,13 @@
         <v>21</v>
       </c>
       <c r="C395" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D395" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E395" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7517,13 +7490,13 @@
         <v>21</v>
       </c>
       <c r="C396" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D396" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E396" t="s">
-        <v>136</v>
+        <v>71</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7534,13 +7507,13 @@
         <v>21</v>
       </c>
       <c r="C397" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D397" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E397" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7551,13 +7524,13 @@
         <v>21</v>
       </c>
       <c r="C398" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D398" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E398" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7568,13 +7541,13 @@
         <v>21</v>
       </c>
       <c r="C399" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D399" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E399" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7585,13 +7558,13 @@
         <v>21</v>
       </c>
       <c r="C400" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D400" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E400" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7602,13 +7575,13 @@
         <v>21</v>
       </c>
       <c r="C401" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D401" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E401" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7619,13 +7592,13 @@
         <v>21</v>
       </c>
       <c r="C402" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D402" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E402" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7636,13 +7609,13 @@
         <v>21</v>
       </c>
       <c r="C403" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D403" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E403" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7653,13 +7626,13 @@
         <v>21</v>
       </c>
       <c r="C404" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D404" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E404" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7670,13 +7643,13 @@
         <v>21</v>
       </c>
       <c r="C405" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D405" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E405" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7687,13 +7660,13 @@
         <v>21</v>
       </c>
       <c r="C406" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D406" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E406" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7704,13 +7677,13 @@
         <v>21</v>
       </c>
       <c r="C407" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D407" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E407" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7721,13 +7694,13 @@
         <v>21</v>
       </c>
       <c r="C408" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D408" t="s">
         <v>52</v>
       </c>
       <c r="E408" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7738,13 +7711,13 @@
         <v>21</v>
       </c>
       <c r="C409" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D409" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E409" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7755,13 +7728,13 @@
         <v>21</v>
       </c>
       <c r="C410" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D410" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E410" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7772,13 +7745,13 @@
         <v>21</v>
       </c>
       <c r="C411" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D411" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E411" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7789,13 +7762,13 @@
         <v>21</v>
       </c>
       <c r="C412" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D412" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E412" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7806,13 +7779,13 @@
         <v>21</v>
       </c>
       <c r="C413" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D413" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E413" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7823,13 +7796,13 @@
         <v>21</v>
       </c>
       <c r="C414" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D414" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E414" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7840,13 +7813,13 @@
         <v>21</v>
       </c>
       <c r="C415" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D415" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E415" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7857,13 +7830,13 @@
         <v>22</v>
       </c>
       <c r="C416" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D416" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E416" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7874,13 +7847,13 @@
         <v>22</v>
       </c>
       <c r="C417" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D417" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E417" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7891,13 +7864,13 @@
         <v>22</v>
       </c>
       <c r="C418" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D418" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E418" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7908,10 +7881,13 @@
         <v>22</v>
       </c>
       <c r="C419" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D419" t="s">
-        <v>63</v>
+        <v>50</v>
+      </c>
+      <c r="E419" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7922,13 +7898,13 @@
         <v>22</v>
       </c>
       <c r="C420" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D420" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E420" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7939,13 +7915,13 @@
         <v>22</v>
       </c>
       <c r="C421" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D421" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E421" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7956,13 +7932,13 @@
         <v>22</v>
       </c>
       <c r="C422" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D422" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E422" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7973,13 +7949,13 @@
         <v>22</v>
       </c>
       <c r="C423" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D423" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E423" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7990,13 +7966,13 @@
         <v>22</v>
       </c>
       <c r="C424" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D424" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E424" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -8007,13 +7983,13 @@
         <v>22</v>
       </c>
       <c r="C425" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D425" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E425" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -8024,13 +8000,13 @@
         <v>22</v>
       </c>
       <c r="C426" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D426" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E426" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -8041,13 +8017,13 @@
         <v>22</v>
       </c>
       <c r="C427" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D427" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E427" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -8058,13 +8034,13 @@
         <v>22</v>
       </c>
       <c r="C428" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D428" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E428" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -8075,13 +8051,13 @@
         <v>22</v>
       </c>
       <c r="C429" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D429" t="s">
         <v>50</v>
       </c>
       <c r="E429" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -8092,13 +8068,13 @@
         <v>22</v>
       </c>
       <c r="C430" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D430" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E430" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -8109,13 +8085,13 @@
         <v>22</v>
       </c>
       <c r="C431" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D431" t="s">
         <v>52</v>
       </c>
       <c r="E431" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -8126,13 +8102,13 @@
         <v>22</v>
       </c>
       <c r="C432" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D432" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E432" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -8143,13 +8119,13 @@
         <v>22</v>
       </c>
       <c r="C433" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D433" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E433" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -8160,13 +8136,13 @@
         <v>22</v>
       </c>
       <c r="C434" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D434" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E434" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -8177,13 +8153,13 @@
         <v>22</v>
       </c>
       <c r="C435" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D435" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E435" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -8194,13 +8170,13 @@
         <v>22</v>
       </c>
       <c r="C436" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D436" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E436" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -8211,13 +8187,13 @@
         <v>22</v>
       </c>
       <c r="C437" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D437" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E437" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -8228,13 +8204,13 @@
         <v>22</v>
       </c>
       <c r="C438" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D438" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E438" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -8245,13 +8221,13 @@
         <v>23</v>
       </c>
       <c r="C439" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D439" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E439" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -8262,13 +8238,13 @@
         <v>23</v>
       </c>
       <c r="C440" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D440" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E440" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -8279,13 +8255,13 @@
         <v>23</v>
       </c>
       <c r="C441" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D441" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E441" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -8296,13 +8272,13 @@
         <v>23</v>
       </c>
       <c r="C442" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D442" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E442" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -8313,13 +8289,13 @@
         <v>23</v>
       </c>
       <c r="C443" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D443" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E443" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -8330,13 +8306,13 @@
         <v>23</v>
       </c>
       <c r="C444" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D444" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E444" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -8347,13 +8323,13 @@
         <v>23</v>
       </c>
       <c r="C445" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D445" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E445" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -8364,10 +8340,13 @@
         <v>23</v>
       </c>
       <c r="C446" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D446" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="E446" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -8378,13 +8357,13 @@
         <v>23</v>
       </c>
       <c r="C447" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D447" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E447" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -8395,13 +8374,13 @@
         <v>23</v>
       </c>
       <c r="C448" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D448" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E448" t="s">
-        <v>80</v>
+        <v>132</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -8412,13 +8391,13 @@
         <v>23</v>
       </c>
       <c r="C449" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D449" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E449" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8429,13 +8408,13 @@
         <v>23</v>
       </c>
       <c r="C450" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D450" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E450" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8446,13 +8425,13 @@
         <v>23</v>
       </c>
       <c r="C451" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D451" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E451" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8463,10 +8442,13 @@
         <v>23</v>
       </c>
       <c r="C452" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D452" t="s">
-        <v>63</v>
+        <v>49</v>
+      </c>
+      <c r="E452" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8477,13 +8459,13 @@
         <v>23</v>
       </c>
       <c r="C453" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D453" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E453" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8494,13 +8476,13 @@
         <v>23</v>
       </c>
       <c r="C454" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D454" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E454" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8511,13 +8493,13 @@
         <v>23</v>
       </c>
       <c r="C455" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D455" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E455" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8528,13 +8510,13 @@
         <v>23</v>
       </c>
       <c r="C456" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D456" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E456" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8545,13 +8527,13 @@
         <v>23</v>
       </c>
       <c r="C457" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D457" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E457" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8562,13 +8544,13 @@
         <v>23</v>
       </c>
       <c r="C458" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D458" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E458" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8579,13 +8561,13 @@
         <v>23</v>
       </c>
       <c r="C459" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D459" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="E459" t="s">
-        <v>140</v>
+        <v>66</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8596,13 +8578,13 @@
         <v>23</v>
       </c>
       <c r="C460" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D460" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E460" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8613,404 +8595,13 @@
         <v>23</v>
       </c>
       <c r="C461" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D461" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E461" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="462" spans="1:5">
-      <c r="A462" s="1">
-        <v>620</v>
-      </c>
-      <c r="B462" t="s">
-        <v>24</v>
-      </c>
-      <c r="C462" t="s">
-        <v>25</v>
-      </c>
-      <c r="D462" t="s">
-        <v>48</v>
-      </c>
-      <c r="E462" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="463" spans="1:5">
-      <c r="A463" s="1">
-        <v>621</v>
-      </c>
-      <c r="B463" t="s">
-        <v>24</v>
-      </c>
-      <c r="C463" t="s">
-        <v>26</v>
-      </c>
-      <c r="D463" t="s">
-        <v>59</v>
-      </c>
-      <c r="E463" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="464" spans="1:5">
-      <c r="A464" s="1">
-        <v>623</v>
-      </c>
-      <c r="B464" t="s">
-        <v>24</v>
-      </c>
-      <c r="C464" t="s">
-        <v>27</v>
-      </c>
-      <c r="D464" t="s">
-        <v>72</v>
-      </c>
-      <c r="E464" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="465" spans="1:5">
-      <c r="A465" s="1">
-        <v>624</v>
-      </c>
-      <c r="B465" t="s">
-        <v>24</v>
-      </c>
-      <c r="C465" t="s">
-        <v>28</v>
-      </c>
-      <c r="D465" t="s">
-        <v>50</v>
-      </c>
-      <c r="E465" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="466" spans="1:5">
-      <c r="A466" s="1">
-        <v>625</v>
-      </c>
-      <c r="B466" t="s">
-        <v>24</v>
-      </c>
-      <c r="C466" t="s">
-        <v>29</v>
-      </c>
-      <c r="D466" t="s">
-        <v>51</v>
-      </c>
-      <c r="E466" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="467" spans="1:5">
-      <c r="A467" s="1">
-        <v>626</v>
-      </c>
-      <c r="B467" t="s">
-        <v>24</v>
-      </c>
-      <c r="C467" t="s">
-        <v>30</v>
-      </c>
-      <c r="D467" t="s">
-        <v>52</v>
-      </c>
-      <c r="E467" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="468" spans="1:5">
-      <c r="A468" s="1">
-        <v>627</v>
-      </c>
-      <c r="B468" t="s">
-        <v>24</v>
-      </c>
-      <c r="C468" t="s">
-        <v>31</v>
-      </c>
-      <c r="D468" t="s">
-        <v>50</v>
-      </c>
-      <c r="E468" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="469" spans="1:5">
-      <c r="A469" s="1">
-        <v>629</v>
-      </c>
-      <c r="B469" t="s">
-        <v>24</v>
-      </c>
-      <c r="C469" t="s">
-        <v>32</v>
-      </c>
-      <c r="D469" t="s">
-        <v>54</v>
-      </c>
-      <c r="E469" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="470" spans="1:5">
-      <c r="A470" s="1">
-        <v>630</v>
-      </c>
-      <c r="B470" t="s">
-        <v>24</v>
-      </c>
-      <c r="C470" t="s">
-        <v>33</v>
-      </c>
-      <c r="D470" t="s">
-        <v>50</v>
-      </c>
-      <c r="E470" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="471" spans="1:5">
-      <c r="A471" s="1">
-        <v>631</v>
-      </c>
-      <c r="B471" t="s">
-        <v>24</v>
-      </c>
-      <c r="C471" t="s">
-        <v>34</v>
-      </c>
-      <c r="D471" t="s">
-        <v>50</v>
-      </c>
-      <c r="E471" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="472" spans="1:5">
-      <c r="A472" s="1">
-        <v>632</v>
-      </c>
-      <c r="B472" t="s">
-        <v>24</v>
-      </c>
-      <c r="C472" t="s">
-        <v>35</v>
-      </c>
-      <c r="D472" t="s">
-        <v>50</v>
-      </c>
-      <c r="E472" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="473" spans="1:5">
-      <c r="A473" s="1">
-        <v>633</v>
-      </c>
-      <c r="B473" t="s">
-        <v>24</v>
-      </c>
-      <c r="C473" t="s">
-        <v>36</v>
-      </c>
-      <c r="D473" t="s">
-        <v>54</v>
-      </c>
-      <c r="E473" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="474" spans="1:5">
-      <c r="A474" s="1">
-        <v>635</v>
-      </c>
-      <c r="B474" t="s">
-        <v>24</v>
-      </c>
-      <c r="C474" t="s">
-        <v>37</v>
-      </c>
-      <c r="D474" t="s">
-        <v>51</v>
-      </c>
-      <c r="E474" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="475" spans="1:5">
-      <c r="A475" s="1">
-        <v>636</v>
-      </c>
-      <c r="B475" t="s">
-        <v>24</v>
-      </c>
-      <c r="C475" t="s">
-        <v>38</v>
-      </c>
-      <c r="D475" t="s">
-        <v>50</v>
-      </c>
-      <c r="E475" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="476" spans="1:5">
-      <c r="A476" s="1">
-        <v>637</v>
-      </c>
-      <c r="B476" t="s">
-        <v>24</v>
-      </c>
-      <c r="C476" t="s">
-        <v>39</v>
-      </c>
-      <c r="D476" t="s">
-        <v>48</v>
-      </c>
-      <c r="E476" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="477" spans="1:5">
-      <c r="A477" s="1">
-        <v>639</v>
-      </c>
-      <c r="B477" t="s">
-        <v>24</v>
-      </c>
-      <c r="C477" t="s">
-        <v>40</v>
-      </c>
-      <c r="D477" t="s">
-        <v>52</v>
-      </c>
-      <c r="E477" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="478" spans="1:5">
-      <c r="A478" s="1">
-        <v>640</v>
-      </c>
-      <c r="B478" t="s">
-        <v>24</v>
-      </c>
-      <c r="C478" t="s">
-        <v>41</v>
-      </c>
-      <c r="D478" t="s">
-        <v>55</v>
-      </c>
-      <c r="E478" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="479" spans="1:5">
-      <c r="A479" s="1">
-        <v>641</v>
-      </c>
-      <c r="B479" t="s">
-        <v>24</v>
-      </c>
-      <c r="C479" t="s">
-        <v>42</v>
-      </c>
-      <c r="D479" t="s">
-        <v>49</v>
-      </c>
-      <c r="E479" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5">
-      <c r="A480" s="1">
-        <v>642</v>
-      </c>
-      <c r="B480" t="s">
-        <v>24</v>
-      </c>
-      <c r="C480" t="s">
-        <v>43</v>
-      </c>
-      <c r="D480" t="s">
-        <v>56</v>
-      </c>
-      <c r="E480" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="481" spans="1:5">
-      <c r="A481" s="1">
-        <v>643</v>
-      </c>
-      <c r="B481" t="s">
-        <v>24</v>
-      </c>
-      <c r="C481" t="s">
-        <v>44</v>
-      </c>
-      <c r="D481" t="s">
-        <v>62</v>
-      </c>
-      <c r="E481" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="482" spans="1:5">
-      <c r="A482" s="1">
-        <v>645</v>
-      </c>
-      <c r="B482" t="s">
-        <v>24</v>
-      </c>
-      <c r="C482" t="s">
-        <v>45</v>
-      </c>
-      <c r="D482" t="s">
-        <v>48</v>
-      </c>
-      <c r="E482" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="483" spans="1:5">
-      <c r="A483" s="1">
-        <v>647</v>
-      </c>
-      <c r="B483" t="s">
-        <v>24</v>
-      </c>
-      <c r="C483" t="s">
-        <v>46</v>
-      </c>
-      <c r="D483" t="s">
-        <v>50</v>
-      </c>
-      <c r="E483" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="484" spans="1:5">
-      <c r="A484" s="1">
-        <v>648</v>
-      </c>
-      <c r="B484" t="s">
-        <v>24</v>
-      </c>
-      <c r="C484" t="s">
-        <v>47</v>
-      </c>
-      <c r="D484" t="s">
-        <v>51</v>
-      </c>
-      <c r="E484" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
